--- a/Figure_Plot/figure_plot_2_3/settings.xlsx
+++ b/Figure_Plot/figure_plot_2_3/settings.xlsx
@@ -51,14 +51,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -66,7 +66,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
+      <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -102,7 +102,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -165,8 +165,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="DengXian Light"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -217,8 +217,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="DengXian"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
